--- a/Configs/GameConfig/Datas/general.xlsx
+++ b/Configs/GameConfig/Datas/general.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0#"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +455,71 @@
           <t>status</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>combatArchetype</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>rangeCells</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>attackDamage</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>attackIntervalSeconds</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>damageMode</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>targetPolicy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prefabAddress</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>animationKey</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>projectileType</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>projectileSpeed</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>partRecruitWeight</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>skillKey</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +557,71 @@
           <t>string?</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string?</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string?</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,12 +629,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -539,9 +666,73 @@
           <t>状态</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是否进入本期配置快照与配方索引</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pike 或 bow，映射既有逻辑原型</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>当前 Unity 网格攻击范围</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1 级基础伤害</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>基础攻击间隔</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>近战枪击 或 单体，供校验/表现描述</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>复用现有目标策略键</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>当前枪兵/弓兵回退地址，后续可替换为专属 Prefab</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>表现绑定键</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>仅远程武将需要，本期为 SimpleDynamicArrow</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>仅远程武将使用，本期 200</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>每个配方字加入玩家池的权重，首版为 1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>主动技能Key</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
         <v>0</v>
       </c>
@@ -568,9 +759,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
         <v>1</v>
       </c>
@@ -597,9 +805,56 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pike</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>近战枪击</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ZhangFei</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>zhan1</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>BattleShout</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
         <v>2</v>
       </c>
@@ -626,9 +881,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
         <v>3</v>
       </c>
@@ -655,9 +927,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
         <v>4</v>
       </c>
@@ -684,9 +973,61 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>bow</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>nearest</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>HuangZhong</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>zhan1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>SimpleDynamicArrow</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>FireArrowBarrage</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
         <v>5</v>
       </c>
@@ -713,9 +1054,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
         <v>6</v>
       </c>
@@ -742,9 +1100,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
         <v>7</v>
       </c>
@@ -771,9 +1146,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
         <v>8</v>
       </c>
@@ -800,9 +1192,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
         <v>9</v>
       </c>
@@ -829,9 +1238,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
         <v>10</v>
       </c>
@@ -858,9 +1284,26 @@
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
       </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
         <v>11</v>
       </c>
@@ -886,6 +1329,24 @@
         <is>
           <t>PARTIAL_CORE_CONFIG</t>
         </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/general.xlsx
+++ b/Configs/GameConfig/Datas/general.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1626a36ed854256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9f271e4e1daf4d1b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,50 +372,46 @@
         <x:v>partWords</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>weaponType</x:v>
+        <x:v>enabled</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>status</x:v>
+        <x:v>combatArchetype</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>enabled</x:v>
+        <x:v>rangeCells</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>combatArchetype</x:v>
+        <x:v>attackDamage</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>rangeCells</x:v>
+        <x:v>attackIntervalSeconds</x:v>
       </x:c>
       <x:c r="K1" t="str">
-        <x:v>attackDamage</x:v>
+        <x:v>damageMode</x:v>
       </x:c>
       <x:c r="L1" t="str">
-        <x:v>attackIntervalSeconds</x:v>
+        <x:v>targetPolicy</x:v>
       </x:c>
       <x:c r="M1" t="str">
-        <x:v>damageMode</x:v>
+        <x:v>prefabAddress</x:v>
       </x:c>
       <x:c r="N1" t="str">
-        <x:v>targetPolicy</x:v>
+        <x:v>animationKey</x:v>
       </x:c>
       <x:c r="O1" t="str">
-        <x:v>prefabAddress</x:v>
+        <x:v>projectileType</x:v>
       </x:c>
       <x:c r="P1" t="str">
-        <x:v>animationKey</x:v>
+        <x:v>projectileSpeed</x:v>
       </x:c>
       <x:c r="Q1" t="str">
-        <x:v>projectileType</x:v>
+        <x:v>partRecruitWeight</x:v>
       </x:c>
       <x:c r="R1" t="str">
-        <x:v>projectileSpeed</x:v>
-      </x:c>
-      <x:c r="S1" t="str">
-        <x:v>partRecruitWeight</x:v>
-      </x:c>
-      <x:c r="T1" t="str">
         <x:v>skillId</x:v>
       </x:c>
+      <x:c r="S1"/>
+      <x:c r="T1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -434,25 +430,25 @@
         <x:v>(list#sep=,),string</x:v>
       </x:c>
       <x:c r="F2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
         <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>string</x:v>
       </x:c>
       <x:c r="J2" t="str">
         <x:v>float</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>int</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>float</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="M2" t="str">
         <x:v>string</x:v>
@@ -461,23 +457,19 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>string</x:v>
+        <x:v>string?</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>string?</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="R2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="S2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="T2" t="str">
         <x:v>int?</x:v>
       </x:c>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -508,62 +500,58 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
+        <x:v>主键，武将唯一 ID</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>名称</x:v>
+        <x:v>完整名称</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>姓氏</x:v>
+        <x:v>姓氏字</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>名字拆字</x:v>
+        <x:v>名字拆字，严格两个不同的字，按顺序构成合成配方，如 张,飞</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>武器类型</x:v>
+        <x:v>是否进入本期配置快照与配方索引</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>状态</x:v>
+        <x:v>战斗原型，只能填 pike 或 bow</x:v>
       </x:c>
       <x:c r="H4" t="str">
-        <x:v>是否进入本期配置快照与配方索引</x:v>
+        <x:v>攻击范围，格，必须为正</x:v>
       </x:c>
       <x:c r="I4" t="str">
-        <x:v>pike 或 bow，映射既有逻辑原型</x:v>
+        <x:v>1 级基础伤害，必须为正</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>当前 Unity 网格攻击范围</x:v>
+        <x:v>基础攻击间隔，必须为正</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>1 级基础伤害</x:v>
+        <x:v>伤害模式：近战枪击 或 单体</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>基础攻击间隔</x:v>
+        <x:v>选敌策略，复用现有目标策略键</x:v>
       </x:c>
       <x:c r="M4" t="str">
-        <x:v>近战枪击 或 单体，供校验/表现描述</x:v>
+        <x:v>武将 Prefab 地址，如 ZhangFei</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>复用现有目标策略键</x:v>
+        <x:v>Spine 待机动画名，当前统一为 zhan1</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>当前枪兵/弓兵回退地址，后续可替换为专属 Prefab</x:v>
+        <x:v>投射物类型，仅远程武将必填，当前为 SimpleDynamicArrow；枪型留空</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>表现绑定键</x:v>
+        <x:v>投射物速度，仅远程武将使用，当前 200；枪型填 0</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>仅远程武将需要，本期为 SimpleDynamicArrow</x:v>
+        <x:v>每个配方字加入玩家池的权重，必须大于 0</x:v>
       </x:c>
       <x:c r="R4" t="str">
-        <x:v>仅远程武将使用，本期 200</x:v>
-      </x:c>
-      <x:c r="S4" t="str">
-        <x:v>每个配方字加入玩家池的权重，首版为 1</x:v>
-      </x:c>
-      <x:c r="T4" t="str">
-        <x:v>主动技能ID</x:v>
-      </x:c>
+        <x:v>主动技能 ID，引用 skill.Id</x:v>
+      </x:c>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -579,36 +567,32 @@
       <x:c r="E5" t="str">
         <x:v>赵,云</x:v>
       </x:c>
-      <x:c r="F5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H5" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5"/>
+      <x:c r="F5" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5"/>
+      <x:c r="H5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J5" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K5"/>
+      <x:c r="L5" s="1"/>
       <x:c r="M5"/>
       <x:c r="N5"/>
       <x:c r="O5"/>
-      <x:c r="P5"/>
-      <x:c r="Q5"/>
-      <x:c r="R5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S5" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
       <x:c r="T5"/>
     </x:row>
     <x:row r="6">
@@ -625,49 +609,45 @@
       <x:c r="E6" t="str">
         <x:v>张,飞</x:v>
       </x:c>
-      <x:c r="F6" t="n">
+      <x:c r="F6" s="2" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H6" s="2" t="b">
+        <x:v>pike</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J6" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" t="str">
-        <x:v>pike</x:v>
-      </x:c>
-      <x:c r="J6" s="1" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K6" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L6" s="1" t="n">
+      <x:c r="K6" t="str">
+        <x:v>近战枪击</x:v>
+      </x:c>
+      <x:c r="L6" s="1" t="str">
+        <x:v>nearest</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>ZhangFei</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>zhan1</x:v>
+      </x:c>
+      <x:c r="O6"/>
+      <x:c r="P6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M6" t="str">
-        <x:v>近战枪击</x:v>
-      </x:c>
-      <x:c r="N6" t="str">
-        <x:v>nearest</x:v>
-      </x:c>
-      <x:c r="O6" t="str">
-        <x:v>ZhangFei</x:v>
-      </x:c>
-      <x:c r="P6" t="str">
-        <x:v>zhan1</x:v>
-      </x:c>
-      <x:c r="Q6"/>
       <x:c r="R6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T6" t="n">
         <x:v>3</x:v>
       </x:c>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -683,36 +663,32 @@
       <x:c r="E7" t="str">
         <x:v>马,超</x:v>
       </x:c>
-      <x:c r="F7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H7" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7"/>
+      <x:c r="F7" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J7" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K7"/>
+      <x:c r="L7" s="1"/>
       <x:c r="M7"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
-      <x:c r="P7"/>
-      <x:c r="Q7"/>
-      <x:c r="R7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S7" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
       <x:c r="T7"/>
     </x:row>
     <x:row r="8">
@@ -729,36 +705,32 @@
       <x:c r="E8" t="str">
         <x:v>关,羽</x:v>
       </x:c>
-      <x:c r="F8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H8" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8"/>
+      <x:c r="F8" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J8" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L8" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K8"/>
+      <x:c r="L8" s="1"/>
       <x:c r="M8"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
-      <x:c r="P8"/>
-      <x:c r="Q8"/>
-      <x:c r="R8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S8" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
       <x:c r="T8"/>
     </x:row>
     <x:row r="9">
@@ -775,51 +747,47 @@
       <x:c r="E9" t="str">
         <x:v>黄,忠</x:v>
       </x:c>
-      <x:c r="F9" t="n">
-        <x:v>0</x:v>
+      <x:c r="F9" s="2" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H9" s="2" t="b">
+        <x:v>bow</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J9" s="1" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>单体</x:v>
+      </x:c>
+      <x:c r="L9" s="1" t="str">
+        <x:v>nearest</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>HuangZhong</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>zhan1</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>SimpleDynamicArrow</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" t="str">
-        <x:v>bow</x:v>
-      </x:c>
-      <x:c r="J9" s="1" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K9" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L9" s="1" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="M9" t="str">
-        <x:v>单体</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
-        <x:v>nearest</x:v>
-      </x:c>
-      <x:c r="O9" t="str">
-        <x:v>HuangZhong</x:v>
-      </x:c>
-      <x:c r="P9" t="str">
-        <x:v>zhan1</x:v>
-      </x:c>
-      <x:c r="Q9" t="str">
-        <x:v>SimpleDynamicArrow</x:v>
-      </x:c>
       <x:c r="R9" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="S9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T9" t="n">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
@@ -835,36 +803,32 @@
       <x:c r="E10" t="str">
         <x:v>关,平</x:v>
       </x:c>
-      <x:c r="F10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H10" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10"/>
+      <x:c r="F10" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J10" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K10"/>
+      <x:c r="L10" s="1"/>
       <x:c r="M10"/>
       <x:c r="N10"/>
       <x:c r="O10"/>
-      <x:c r="P10"/>
-      <x:c r="Q10"/>
-      <x:c r="R10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S10" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10"/>
+      <x:c r="S10"/>
       <x:c r="T10"/>
     </x:row>
     <x:row r="11">
@@ -881,36 +845,32 @@
       <x:c r="E11" t="str">
         <x:v>关,兴</x:v>
       </x:c>
-      <x:c r="F11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H11" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11"/>
+      <x:c r="F11" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J11" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L11" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K11"/>
+      <x:c r="L11" s="1"/>
       <x:c r="M11"/>
       <x:c r="N11"/>
       <x:c r="O11"/>
-      <x:c r="P11"/>
-      <x:c r="Q11"/>
-      <x:c r="R11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11"/>
+      <x:c r="S11"/>
       <x:c r="T11"/>
     </x:row>
     <x:row r="12">
@@ -927,36 +887,32 @@
       <x:c r="E12" t="str">
         <x:v>张,苞</x:v>
       </x:c>
-      <x:c r="F12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H12" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12"/>
+      <x:c r="F12" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J12" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K12"/>
+      <x:c r="L12" s="1"/>
       <x:c r="M12"/>
       <x:c r="N12"/>
       <x:c r="O12"/>
-      <x:c r="P12"/>
-      <x:c r="Q12"/>
-      <x:c r="R12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S12" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12"/>
+      <x:c r="S12"/>
       <x:c r="T12"/>
     </x:row>
     <x:row r="13">
@@ -973,36 +929,32 @@
       <x:c r="E13" t="str">
         <x:v>张,翼</x:v>
       </x:c>
-      <x:c r="F13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H13" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13"/>
+      <x:c r="F13" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J13" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K13"/>
+      <x:c r="L13" s="1"/>
       <x:c r="M13"/>
       <x:c r="N13"/>
       <x:c r="O13"/>
-      <x:c r="P13"/>
-      <x:c r="Q13"/>
-      <x:c r="R13" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S13" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
       <x:c r="T13"/>
     </x:row>
     <x:row r="14">
@@ -1019,36 +971,32 @@
       <x:c r="E14" t="str">
         <x:v>黄,盖</x:v>
       </x:c>
-      <x:c r="F14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H14" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14"/>
+      <x:c r="F14" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J14" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K14"/>
+      <x:c r="L14" s="1"/>
       <x:c r="M14"/>
       <x:c r="N14"/>
       <x:c r="O14"/>
-      <x:c r="P14"/>
-      <x:c r="Q14"/>
-      <x:c r="R14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S14" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14"/>
+      <x:c r="S14"/>
       <x:c r="T14"/>
     </x:row>
     <x:row r="15">
@@ -1065,36 +1013,32 @@
       <x:c r="E15" t="str">
         <x:v>刘,备</x:v>
       </x:c>
-      <x:c r="F15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H15" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15"/>
+      <x:c r="F15" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J15" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K15"/>
+      <x:c r="L15" s="1"/>
       <x:c r="M15"/>
       <x:c r="N15"/>
       <x:c r="O15"/>
-      <x:c r="P15"/>
-      <x:c r="Q15"/>
-      <x:c r="R15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S15" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15"/>
+      <x:c r="S15"/>
       <x:c r="T15"/>
     </x:row>
     <x:row r="16">
@@ -1111,36 +1055,32 @@
       <x:c r="E16" t="str">
         <x:v>黄,祖</x:v>
       </x:c>
-      <x:c r="F16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" t="str">
-        <x:v>PARTIAL_CORE_CONFIG</x:v>
-      </x:c>
-      <x:c r="H16" s="2" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16"/>
+      <x:c r="F16" s="2" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J16" s="1" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K16"/>
+      <x:c r="L16" s="1"/>
       <x:c r="M16"/>
       <x:c r="N16"/>
       <x:c r="O16"/>
-      <x:c r="P16"/>
-      <x:c r="Q16"/>
-      <x:c r="R16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S16" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16"/>
+      <x:c r="S16"/>
       <x:c r="T16"/>
     </x:row>
   </x:sheetData>
